--- a/SGC-CKN/Excel/4b23c82b-ed92-4a8d-bf5d-a3eab67f3d48_Lô_đất_ký_hiệu_CT-02_P1-164_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/4b23c82b-ed92-4a8d-bf5d-a3eab67f3d48_Lô_đất_ký_hiệu_CT-02_P1-164_D800_19-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="65">
   <si>
     <t>Dự án</t>
   </si>
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>00:20 19/03/2026</t>
+    <t>00:20 20/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -145,8 +145,12 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
+    <t xml:space="preserve">16:40
+19/03/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">17:45
-18/03/2026</t>
+19/03/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -156,7 +160,7 @@
   </si>
   <si>
     <t xml:space="preserve">18:50
-18/03/2026</t>
+19/03/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -166,7 +170,7 @@
   </si>
   <si>
     <t xml:space="preserve">22:30
-18/03/2026</t>
+19/03/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -176,11 +180,11 @@
   </si>
   <si>
     <t xml:space="preserve">22:55
-18/03/2026</t>
+19/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">00:20
-19/03/2026</t>
+20/03/2026</t>
   </si>
   <si>
     <t>Có ghi chú bổ sung Sét tại độ sâu 36,2m</t>
@@ -1286,10 +1290,10 @@
         <v>41</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F15" s="19">
         <v>-14.8</v>
@@ -1312,19 +1316,19 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F16" s="22">
         <v>-20</v>
@@ -1347,19 +1351,19 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E17" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F17" s="25">
         <v>-24</v>
@@ -1382,19 +1386,19 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E18" s="30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F18" s="28">
         <v>-30</v>
@@ -1412,12 +1416,12 @@
         <v>10.09</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="31"/>
       <c r="C21" s="31"/>
@@ -1523,31 +1527,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1703,7 +1707,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
@@ -1732,7 +1736,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
@@ -1761,7 +1765,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1784,7 +1788,7 @@
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B10" s="33" t="s">
         <v>30</v>

--- a/SGC-CKN/Excel/4b23c82b-ed92-4a8d-bf5d-a3eab67f3d48_Lô_đất_ký_hiệu_CT-02_P1-164_D800_19-03-2026.xlsx
+++ b/SGC-CKN/Excel/4b23c82b-ed92-4a8d-bf5d-a3eab67f3d48_Lô_đất_ký_hiệu_CT-02_P1-164_D800_19-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="64">
   <si>
     <t>Dự án</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Tên Máy khoan</t>
   </si>
   <si>
-    <t>SGC-KCN0003</t>
+    <t>SGCT-KCN0003</t>
   </si>
   <si>
     <t>Đường kính</t>
@@ -136,17 +136,13 @@
   </si>
   <si>
     <t xml:space="preserve">16:40
-18/03/2026</t>
+19/03/2026</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:40
-19/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">17:45
@@ -224,7 +220,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -275,6 +271,12 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <color rgb="FF4C1D95"/>
       <sz val="10"/>
       <name val="Arial"/>
@@ -307,7 +309,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -357,6 +359,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFECACA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -472,7 +479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -531,12 +538,6 @@
     <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -564,13 +565,22 @@
     <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1267,172 +1277,172 @@
         <v>-14.8</v>
       </c>
       <c r="H14" s="16">
-        <v>1.67</v>
+        <v>25.67</v>
       </c>
       <c r="I14" s="16">
         <v>7.8</v>
       </c>
-      <c r="J14" s="8">
-        <v>4.68</v>
+      <c r="J14" s="19">
+        <v>0.3</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="F15" s="19">
+      <c r="F15" s="20">
         <v>-14.8</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="20">
         <v>-20</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="20">
         <v>1.08</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="20">
         <v>5.2</v>
       </c>
       <c r="J15" s="8">
         <v>4.8</v>
       </c>
-      <c r="K15" s="20" t="s">
+      <c r="K15" s="21" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="23" t="s">
+      <c r="D16" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="F16" s="22">
+      <c r="F16" s="23">
         <v>-20</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="23">
         <v>-24</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="23">
         <v>1.08</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="23">
         <v>4</v>
       </c>
       <c r="J16" s="8">
         <v>3.69</v>
       </c>
-      <c r="K16" s="23" t="s">
+      <c r="K16" s="24" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="25" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="26" t="s">
+      <c r="D17" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <v>-24</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="26">
         <v>-30</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="26">
         <v>3.67</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="26">
         <v>6</v>
       </c>
       <c r="J17" s="8">
         <v>1.64</v>
       </c>
-      <c r="K17" s="26" t="s">
+      <c r="K17" s="27" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="29" t="s">
+      <c r="D18" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="E18" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" s="28">
+      <c r="F18" s="29">
         <v>-30</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="29">
         <v>-44.3</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="29">
         <v>1.42</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="29">
         <v>14.3</v>
       </c>
       <c r="J18" s="12">
         <v>10.09</v>
       </c>
-      <c r="K18" s="29" t="s">
+      <c r="K18" s="30" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="32" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="21" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
+      <c r="B21" s="32"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
     </row>
     <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -1527,31 +1537,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1661,38 +1671,38 @@
         <v>-14.8</v>
       </c>
       <c r="G5" s="16">
-        <v>1.67</v>
+        <v>25.67</v>
       </c>
       <c r="H5" s="16">
         <v>7.8</v>
       </c>
-      <c r="I5" s="8">
-        <v>4.68</v>
+      <c r="I5" s="19">
+        <v>0.3</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
+      <c r="A6" s="20">
         <v>5</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <v>1</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <v>-14.8</v>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="20">
         <v>-20</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="20">
         <v>1.08</v>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="20">
         <v>5.2</v>
       </c>
       <c r="I6" s="8">
@@ -1700,28 +1710,28 @@
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="22">
+      <c r="A7" s="23">
         <v>6</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="22">
+      <c r="C7" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="23">
         <v>1</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="23">
         <v>-20</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="23">
         <v>-24</v>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="23">
         <v>1.08</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="23">
         <v>4</v>
       </c>
       <c r="I7" s="8">
@@ -1729,28 +1739,28 @@
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="26">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="25">
+      <c r="C8" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="26">
         <v>1</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <v>-24</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <v>-30</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="26">
         <v>3.67</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="26">
         <v>6</v>
       </c>
       <c r="I8" s="8">
@@ -1758,28 +1768,28 @@
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
+      <c r="A9" s="29">
         <v>8</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="28">
+      <c r="C9" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="29">
         <v>1</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <v>-30</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="29">
         <v>-44.3</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="29">
         <v>1.42</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="29">
         <v>14.3</v>
       </c>
       <c r="I9" s="12">
@@ -1787,32 +1797,32 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10" s="33" t="s">
+      <c r="A10" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B10" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <v>8</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="34">
         <v>0</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="34">
         <v>-44.3</v>
       </c>
-      <c r="G10" s="33">
-        <v>10.42</v>
-      </c>
-      <c r="H10" s="33">
+      <c r="G10" s="34">
+        <v>34.42</v>
+      </c>
+      <c r="H10" s="34">
         <v>44.3</v>
       </c>
-      <c r="I10" s="33">
-        <v>4.25</v>
+      <c r="I10" s="34">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>
